--- a/artfynd/A 23188-2022 artfynd.xlsx
+++ b/artfynd/A 23188-2022 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134316956</v>
+        <v>134316950</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>92230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610899</v>
+        <v>610915</v>
       </c>
       <c r="R3" t="n">
-        <v>7204471</v>
+        <v>7204467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134316950</v>
+        <v>134316956</v>
       </c>
       <c r="B4" t="n">
-        <v>92230</v>
+        <v>80474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610915</v>
+        <v>610899</v>
       </c>
       <c r="R4" t="n">
-        <v>7204467</v>
+        <v>7204471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1059,10 +1059,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134316933</v>
+        <v>134316976</v>
       </c>
       <c r="B6" t="n">
-        <v>83344</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1070,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610744</v>
+        <v>610703</v>
       </c>
       <c r="R6" t="n">
-        <v>7204508</v>
+        <v>7204586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134316976</v>
+        <v>134316933</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>83344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610703</v>
+        <v>610744</v>
       </c>
       <c r="R7" t="n">
-        <v>7204586</v>
+        <v>7204508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,32 +1253,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134316932</v>
+        <v>134316949</v>
       </c>
       <c r="B8" t="n">
-        <v>83344</v>
+        <v>80368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610719</v>
+        <v>610660</v>
       </c>
       <c r="R8" t="n">
-        <v>7204505</v>
+        <v>7204630</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,32 +1447,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134316949</v>
+        <v>134316932</v>
       </c>
       <c r="B10" t="n">
-        <v>80368</v>
+        <v>83344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610660</v>
+        <v>610719</v>
       </c>
       <c r="R10" t="n">
-        <v>7204630</v>
+        <v>7204505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 23188-2022 artfynd.xlsx
+++ b/artfynd/A 23188-2022 artfynd.xlsx
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134316959</v>
+        <v>134316971</v>
       </c>
       <c r="B15" t="n">
-        <v>80474</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,23 +1943,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1967,10 +1963,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>610766</v>
+        <v>610894</v>
       </c>
       <c r="R15" t="n">
-        <v>7204209</v>
+        <v>7204472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,10 +2025,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134316971</v>
+        <v>134316966</v>
       </c>
       <c r="B16" t="n">
-        <v>91979</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,19 +2036,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610894</v>
+        <v>610831</v>
       </c>
       <c r="R16" t="n">
-        <v>7204472</v>
+        <v>7204381</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134316966</v>
+        <v>134316959</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>80474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610831</v>
+        <v>610766</v>
       </c>
       <c r="R17" t="n">
-        <v>7204381</v>
+        <v>7204209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 23188-2022 artfynd.xlsx
+++ b/artfynd/A 23188-2022 artfynd.xlsx
@@ -1253,32 +1253,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134316949</v>
+        <v>134316968</v>
       </c>
       <c r="B8" t="n">
-        <v>80368</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610660</v>
+        <v>610893</v>
       </c>
       <c r="R8" t="n">
-        <v>7204630</v>
+        <v>7204467</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134316968</v>
+        <v>134316932</v>
       </c>
       <c r="B9" t="n">
-        <v>91974</v>
+        <v>83344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610893</v>
+        <v>610719</v>
       </c>
       <c r="R9" t="n">
-        <v>7204467</v>
+        <v>7204505</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,32 +1447,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134316932</v>
+        <v>134316949</v>
       </c>
       <c r="B10" t="n">
-        <v>83344</v>
+        <v>80368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610719</v>
+        <v>610660</v>
       </c>
       <c r="R10" t="n">
-        <v>7204505</v>
+        <v>7204630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134316979</v>
+        <v>134316969</v>
       </c>
       <c r="B11" t="n">
-        <v>79025</v>
+        <v>91960</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610940</v>
+        <v>610770</v>
       </c>
       <c r="R11" t="n">
-        <v>7204406</v>
+        <v>7204213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134316969</v>
+        <v>134316979</v>
       </c>
       <c r="B12" t="n">
-        <v>91960</v>
+        <v>79025</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>610770</v>
+        <v>610940</v>
       </c>
       <c r="R12" t="n">
-        <v>7204213</v>
+        <v>7204406</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134316966</v>
+        <v>134316959</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>80474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610831</v>
+        <v>610766</v>
       </c>
       <c r="R16" t="n">
-        <v>7204381</v>
+        <v>7204209</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134316959</v>
+        <v>134316966</v>
       </c>
       <c r="B17" t="n">
-        <v>80474</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610766</v>
+        <v>610831</v>
       </c>
       <c r="R17" t="n">
-        <v>7204209</v>
+        <v>7204381</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 23188-2022 artfynd.xlsx
+++ b/artfynd/A 23188-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134316980</v>
       </c>
       <c r="B2" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>134316950</v>
       </c>
       <c r="B3" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>134316956</v>
       </c>
       <c r="B4" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>134316970</v>
       </c>
       <c r="B5" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134316933</v>
+        <v>134316976</v>
       </c>
       <c r="B6" t="n">
-        <v>83344</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1070,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610744</v>
+        <v>610703</v>
       </c>
       <c r="R6" t="n">
-        <v>7204508</v>
+        <v>7204586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134316976</v>
+        <v>134316933</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>83351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610703</v>
+        <v>610744</v>
       </c>
       <c r="R7" t="n">
-        <v>7204586</v>
+        <v>7204508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,32 +1253,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134316968</v>
+        <v>134316949</v>
       </c>
       <c r="B8" t="n">
-        <v>91974</v>
+        <v>80375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610893</v>
+        <v>610660</v>
       </c>
       <c r="R8" t="n">
-        <v>7204467</v>
+        <v>7204630</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134316932</v>
+        <v>134316968</v>
       </c>
       <c r="B9" t="n">
-        <v>83344</v>
+        <v>91981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610719</v>
+        <v>610893</v>
       </c>
       <c r="R9" t="n">
-        <v>7204505</v>
+        <v>7204467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,32 +1447,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134316949</v>
+        <v>134316932</v>
       </c>
       <c r="B10" t="n">
-        <v>80368</v>
+        <v>83351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610660</v>
+        <v>610719</v>
       </c>
       <c r="R10" t="n">
-        <v>7204630</v>
+        <v>7204505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
         <v>134316969</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>134316979</v>
       </c>
       <c r="B12" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>134316940</v>
       </c>
       <c r="B13" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>134316978</v>
       </c>
       <c r="B14" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>134316971</v>
       </c>
       <c r="B15" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134316959</v>
+        <v>134316966</v>
       </c>
       <c r="B16" t="n">
-        <v>80474</v>
+        <v>79123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610766</v>
+        <v>610831</v>
       </c>
       <c r="R16" t="n">
-        <v>7204209</v>
+        <v>7204381</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134316966</v>
+        <v>134316959</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>80481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610831</v>
+        <v>610766</v>
       </c>
       <c r="R17" t="n">
-        <v>7204381</v>
+        <v>7204209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
         <v>134316957</v>
       </c>
       <c r="B18" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 23188-2022 artfynd.xlsx
+++ b/artfynd/A 23188-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134316980</v>
+        <v>134316979</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610820</v>
+        <v>610940</v>
       </c>
       <c r="R2" t="n">
-        <v>7204359</v>
+        <v>7204406</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134316950</v>
+        <v>134316980</v>
       </c>
       <c r="B3" t="n">
-        <v>92238</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610915</v>
+        <v>610820</v>
       </c>
       <c r="R3" t="n">
-        <v>7204467</v>
+        <v>7204359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134316956</v>
+        <v>134316950</v>
       </c>
       <c r="B4" t="n">
-        <v>80481</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610899</v>
+        <v>610915</v>
       </c>
       <c r="R4" t="n">
-        <v>7204471</v>
+        <v>7204467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134316970</v>
+        <v>134316940</v>
       </c>
       <c r="B5" t="n">
-        <v>91987</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,19 +977,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -997,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610770</v>
+        <v>610685</v>
       </c>
       <c r="R5" t="n">
-        <v>7204213</v>
+        <v>7204558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134316976</v>
+        <v>134316969</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610703</v>
+        <v>610770</v>
       </c>
       <c r="R6" t="n">
-        <v>7204586</v>
+        <v>7204213</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134316933</v>
+        <v>134316968</v>
       </c>
       <c r="B7" t="n">
-        <v>83351</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1191,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610744</v>
+        <v>610893</v>
       </c>
       <c r="R7" t="n">
-        <v>7204508</v>
+        <v>7204467</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134316949</v>
+        <v>134316978</v>
       </c>
       <c r="B8" t="n">
-        <v>80375</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1288,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610660</v>
+        <v>610716</v>
       </c>
       <c r="R8" t="n">
-        <v>7204630</v>
+        <v>7204496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134316968</v>
+        <v>134316976</v>
       </c>
       <c r="B9" t="n">
-        <v>91981</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1385,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610893</v>
+        <v>610703</v>
       </c>
       <c r="R9" t="n">
-        <v>7204467</v>
+        <v>7204586</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,7 +1454,7 @@
         <v>134316932</v>
       </c>
       <c r="B10" t="n">
-        <v>83351</v>
+        <v>83358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134316969</v>
+        <v>134316933</v>
       </c>
       <c r="B11" t="n">
-        <v>91967</v>
+        <v>83358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610770</v>
+        <v>610744</v>
       </c>
       <c r="R11" t="n">
-        <v>7204213</v>
+        <v>7204508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134316979</v>
+        <v>134316966</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>610940</v>
+        <v>610831</v>
       </c>
       <c r="R12" t="n">
-        <v>7204406</v>
+        <v>7204381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134316940</v>
+        <v>134316949</v>
       </c>
       <c r="B13" t="n">
-        <v>91967</v>
+        <v>80382</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>610685</v>
+        <v>610660</v>
       </c>
       <c r="R13" t="n">
-        <v>7204558</v>
+        <v>7204630</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1835,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134316978</v>
+        <v>134316956</v>
       </c>
       <c r="B14" t="n">
-        <v>83215</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610716</v>
+        <v>610899</v>
       </c>
       <c r="R14" t="n">
-        <v>7204496</v>
+        <v>7204471</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1932,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134316971</v>
+        <v>134316957</v>
       </c>
       <c r="B15" t="n">
-        <v>91987</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,19 +1947,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1963,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>610894</v>
+        <v>610743</v>
       </c>
       <c r="R15" t="n">
-        <v>7204472</v>
+        <v>7204542</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2025,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134316966</v>
+        <v>134316958</v>
       </c>
       <c r="B16" t="n">
-        <v>79123</v>
+        <v>80488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2060,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610831</v>
+        <v>610722</v>
       </c>
       <c r="R16" t="n">
-        <v>7204381</v>
+        <v>7204481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2125,7 +2133,7 @@
         <v>134316959</v>
       </c>
       <c r="B17" t="n">
-        <v>80481</v>
+        <v>80488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,103 +2224,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>134316957</v>
-      </c>
-      <c r="B18" t="n">
-        <v>80481</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Liden-Joranträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>610743</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7204542</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
